--- a/data/Escenarios_DET/Swap_costo_variable/elmo_data.xlsx
+++ b/data/Escenarios_DET/Swap_costo_variable/elmo_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_DET\Swap_costo_variable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8548F790-9913-497D-AC8F-EC3CADEDC407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE47C0C7-F4BE-4D0B-A365-325B1E3C8552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="307">
   <si>
     <t>id</t>
   </si>
@@ -946,12 +946,6 @@
   </si>
   <si>
     <t>LH518B_7</t>
-  </si>
-  <si>
-    <t>LH518B_8</t>
-  </si>
-  <si>
-    <t>LH518B_9</t>
   </si>
   <si>
     <t>battery_cost</t>
@@ -1813,7 +1807,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="20" bestFit="1" customWidth="1"/>
@@ -2037,10 +2031,10 @@
         <v>36</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E3" s="18" t="s">
         <v>48</v>
@@ -2129,10 +2123,10 @@
         <v>297</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E4" s="18" t="s">
         <v>48</v>
@@ -2221,10 +2215,10 @@
         <v>298</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E5" s="18" t="s">
         <v>48</v>
@@ -2313,10 +2307,10 @@
         <v>299</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E6" s="18" t="s">
         <v>48</v>
@@ -2405,10 +2399,10 @@
         <v>300</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E7" s="18" t="s">
         <v>48</v>
@@ -2497,10 +2491,10 @@
         <v>301</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E8" s="18" t="s">
         <v>48</v>
@@ -2589,10 +2583,10 @@
         <v>302</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E9" s="18" t="s">
         <v>48</v>
@@ -2670,190 +2664,6 @@
         <v>0.95</v>
       </c>
       <c r="AD9" s="65">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="28">
-        <v>8</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>308</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="G10" s="6">
-        <v>18</v>
-      </c>
-      <c r="H10" s="63">
-        <v>0.84</v>
-      </c>
-      <c r="I10" s="64">
-        <v>20</v>
-      </c>
-      <c r="J10" s="64">
-        <v>20</v>
-      </c>
-      <c r="K10" s="61">
-        <v>54.8</v>
-      </c>
-      <c r="L10" s="6">
-        <v>540</v>
-      </c>
-      <c r="M10" s="19">
-        <v>8.73</v>
-      </c>
-      <c r="N10" s="58">
-        <v>-1</v>
-      </c>
-      <c r="O10" s="58">
-        <v>-1</v>
-      </c>
-      <c r="P10" s="58">
-        <v>-1</v>
-      </c>
-      <c r="Q10" s="58">
-        <v>-1</v>
-      </c>
-      <c r="R10" s="32">
-        <v>0.95</v>
-      </c>
-      <c r="S10" s="23">
-        <v>0.92</v>
-      </c>
-      <c r="T10" s="25">
-        <v>15</v>
-      </c>
-      <c r="U10" s="66">
-        <v>0.47</v>
-      </c>
-      <c r="V10" s="31">
-        <v>160</v>
-      </c>
-      <c r="W10" s="65">
-        <v>4</v>
-      </c>
-      <c r="X10" s="57">
-        <v>320</v>
-      </c>
-      <c r="Y10" s="67">
-        <v>4</v>
-      </c>
-      <c r="Z10" s="57">
-        <v>482</v>
-      </c>
-      <c r="AA10" s="57">
-        <v>0.2</v>
-      </c>
-      <c r="AB10" s="65">
-        <v>0.95</v>
-      </c>
-      <c r="AC10" s="65">
-        <v>0.95</v>
-      </c>
-      <c r="AD10" s="65">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="28">
-        <v>9</v>
-      </c>
-      <c r="B11" s="33" t="s">
-        <v>304</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>308</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="G11" s="6">
-        <v>18</v>
-      </c>
-      <c r="H11" s="63">
-        <v>0.84</v>
-      </c>
-      <c r="I11" s="64">
-        <v>20</v>
-      </c>
-      <c r="J11" s="64">
-        <v>20</v>
-      </c>
-      <c r="K11" s="61">
-        <v>54.8</v>
-      </c>
-      <c r="L11" s="6">
-        <v>540</v>
-      </c>
-      <c r="M11" s="19">
-        <v>8.73</v>
-      </c>
-      <c r="N11" s="58">
-        <v>-1</v>
-      </c>
-      <c r="O11" s="58">
-        <v>-1</v>
-      </c>
-      <c r="P11" s="58">
-        <v>-1</v>
-      </c>
-      <c r="Q11" s="58">
-        <v>-1</v>
-      </c>
-      <c r="R11" s="32">
-        <v>0.95</v>
-      </c>
-      <c r="S11" s="23">
-        <v>0.92</v>
-      </c>
-      <c r="T11" s="25">
-        <v>15</v>
-      </c>
-      <c r="U11" s="66">
-        <v>0.47</v>
-      </c>
-      <c r="V11" s="31">
-        <v>160</v>
-      </c>
-      <c r="W11" s="65">
-        <v>4</v>
-      </c>
-      <c r="X11" s="57">
-        <v>320</v>
-      </c>
-      <c r="Y11" s="67">
-        <v>4</v>
-      </c>
-      <c r="Z11" s="57">
-        <v>482</v>
-      </c>
-      <c r="AA11" s="57">
-        <v>0.2</v>
-      </c>
-      <c r="AB11" s="65">
-        <v>0.95</v>
-      </c>
-      <c r="AC11" s="65">
-        <v>0.95</v>
-      </c>
-      <c r="AD11" s="65">
         <v>8</v>
       </c>
     </row>
@@ -2895,7 +2705,7 @@
         <v>61</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H1" s="9" t="s">
         <v>71</v>
@@ -2968,6 +2778,7 @@
     <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2990,7 +2801,7 @@
         <v>69</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H1" s="9" t="s">
         <v>49</v>
@@ -3045,7 +2856,7 @@
         <v>79000</v>
       </c>
       <c r="H3" s="31" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
